--- a/data/Coordinate_Uma.xlsx
+++ b/data/Coordinate_Uma.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LOQ\Desktop\WEB GIS DGHC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LOQ\Desktop\WEB GIS DGHC\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B960D064-AC6C-4670-B246-82507FC244E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D71ED0-1941-4F37-ACC8-76BB790C4AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="79">
   <si>
     <t>ID_UMA</t>
   </si>
@@ -59,15 +59,6 @@
     <t>001</t>
   </si>
   <si>
-    <t>Viqueque</t>
-  </si>
-  <si>
-    <t>Caraubalo</t>
-  </si>
-  <si>
-    <t>Lamaclaran</t>
-  </si>
-  <si>
     <t>UMA DIGNU</t>
   </si>
   <si>
@@ -80,18 +71,12 @@
     <t>002</t>
   </si>
   <si>
-    <t>Manehat</t>
-  </si>
-  <si>
     <t>02.jpg</t>
   </si>
   <si>
     <t>003</t>
   </si>
   <si>
-    <t>Cabira Oan</t>
-  </si>
-  <si>
     <t>VULNERABLE</t>
   </si>
   <si>
@@ -101,12 +86,6 @@
     <t>004</t>
   </si>
   <si>
-    <t>Uma Uain Craic</t>
-  </si>
-  <si>
-    <t>Naeboruc</t>
-  </si>
-  <si>
     <t>04.jpg</t>
   </si>
   <si>
@@ -267,6 +246,18 @@
   </si>
   <si>
     <t>Uma Komersial</t>
+  </si>
+  <si>
+    <t>Manufahi</t>
+  </si>
+  <si>
+    <t>Fatuberliu</t>
+  </si>
+  <si>
+    <t>Clacuc</t>
+  </si>
+  <si>
+    <t>Webicas</t>
   </si>
 </sst>
 </file>
@@ -674,7 +665,9 @@
     <col min="4" max="4" width="19" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="9" width="14" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="19" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
   </cols>
@@ -719,31 +712,31 @@
         <v>11</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="G2" s="4">
         <v>-9.0515100000000004</v>
       </c>
       <c r="H2" s="4">
-        <v>126.03048</v>
+        <v>12603048</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="K2" s="2">
         <v>2024</v>
@@ -751,34 +744,34 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>12</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="G3" s="7">
         <v>-9.0509699999999995</v>
       </c>
       <c r="H3" s="7">
-        <v>126.0303</v>
+        <v>1260303</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="K3" s="5">
         <v>2024</v>
@@ -786,34 +779,34 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G4" s="4">
         <v>-9.0496099999999995</v>
       </c>
       <c r="H4" s="4">
-        <v>126.03234999999999</v>
+        <v>12603235</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="K4" s="2">
         <v>2023</v>
@@ -821,34 +814,34 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>27</v>
+        <v>20</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G5" s="7">
         <v>-9.0492100000000004</v>
       </c>
       <c r="H5" s="7">
-        <v>126.03197</v>
+        <v>12603197</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="K5" s="5">
         <v>2024</v>
@@ -856,34 +849,34 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G6" s="4">
         <v>-8.5568899999999992</v>
       </c>
       <c r="H6" s="4">
-        <v>125.57890999999999</v>
+        <v>12557891</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K6" s="2">
         <v>2024</v>
@@ -891,34 +884,34 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" s="5" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G7" s="7">
         <v>-8.5620999999999992</v>
       </c>
       <c r="H7" s="7">
-        <v>125.5812</v>
+        <v>1255812</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="K7" s="5">
         <v>2025</v>
@@ -926,34 +919,34 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G8" s="4">
         <v>-8.7234499999999997</v>
       </c>
       <c r="H8" s="4">
-        <v>125.56789000000001</v>
+        <v>12556789</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="K8" s="2">
         <v>2023</v>
@@ -961,34 +954,34 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G9" s="7">
         <v>-8.4712300000000003</v>
       </c>
       <c r="H9" s="7">
-        <v>126.45612</v>
+        <v>12645612</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="K9" s="5">
         <v>2024</v>
@@ -1012,16 +1005,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -1029,13 +1022,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -1043,13 +1036,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1057,13 +1050,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1071,13 +1064,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -1085,13 +1078,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="D6" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -1099,13 +1092,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -1113,13 +1106,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -1127,13 +1120,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -1141,13 +1134,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -1155,13 +1148,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -1169,13 +1162,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
